--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.26264106446414</v>
+        <v>8.980179172975424</v>
       </c>
       <c r="D2" t="n">
-        <v>55.96759014978752</v>
+        <v>9.094733399340472</v>
       </c>
       <c r="E2" t="n">
-        <v>13.10407700564327</v>
+        <v>2.129412513417031</v>
       </c>
       <c r="F2" t="n">
-        <v>13.61637793220132</v>
+        <v>2.212661413982714</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.84703770712299</v>
+        <v>7.775143627407486</v>
       </c>
       <c r="D3" t="n">
-        <v>48.13771630484014</v>
+        <v>7.822378899536523</v>
       </c>
       <c r="E3" t="n">
-        <v>13.10407700564327</v>
+        <v>2.129412513417031</v>
       </c>
       <c r="F3" t="n">
-        <v>13.61637793220132</v>
+        <v>2.212661413982714</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.50890856618279</v>
+        <v>3.982697642004704</v>
       </c>
       <c r="D4" t="n">
-        <v>23.97515916809298</v>
+        <v>3.895963364815109</v>
       </c>
       <c r="E4" t="n">
-        <v>13.10407700564327</v>
+        <v>2.129412513417031</v>
       </c>
       <c r="F4" t="n">
-        <v>13.61637793220132</v>
+        <v>2.212661413982714</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
